--- a/docs/downloads/经营分_山西省区__山西中片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_山西省区__山西中片区_2026-10-18.xlsx
@@ -878,14 +878,14 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I4" t="n">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -913,7 +913,7 @@
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T4" t="n">
         <v>20</v>
@@ -962,14 +962,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I5" t="n">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
@@ -1028,20 +1028,24 @@
           <t>山西中片区</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>长治市</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>6601152258656716808</t>
+          <t>7234811569874405410</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7天酒店(长治西大街上党门店)</t>
+          <t>7天酒店（长治长子鹿谷大街体育馆店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7天连锁酒店(长治西大街上党门店)</t>
+          <t>7天酒店(长治长子路谷大街体育馆店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1067,13 +1071,13 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P6" t="n">
         <v>30</v>
@@ -1114,22 +1118,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7234811569874405410</t>
+          <t>6988348997492541453</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7天酒店（长治长子鹿谷大街体育馆店）</t>
+          <t>维也纳3好酒店（山西晋中市寿阳朝阳阁店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7天酒店(长治长子路谷大街体育馆店)</t>
+          <t>维也纳3好酒店(山西晋中市寿阳朝阳阁店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1202,31 +1206,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6988348997492541453</t>
+          <t>7122789583427012622</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（山西晋中市寿阳朝阳阁店）</t>
+          <t>7天酒店（新7天长治屯留会堂店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(山西晋中市寿阳朝阳阁店)</t>
+          <t>7天酒店(长治屯留会堂店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>-5</v>
@@ -1243,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
@@ -1255,7 +1259,7 @@
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1295,29 +1299,29 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7122789583427012622</t>
+          <t>6601190874749601800</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7天酒店（新7天长治屯留会堂店）</t>
+          <t>7天酒店（长治沁县店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7天酒店(长治屯留会堂店)</t>
+          <t>7天连锁酒店(沁县店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1331,19 +1335,19 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1378,22 +1382,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601190874749601800</t>
+          <t>7326770712952178688</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7天酒店（长治沁县店）</t>
+          <t>IU酒店（晋中榆次五中万达广场店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7天连锁酒店(沁县店)</t>
+          <t>IU酒店(晋中榆次五中万达广场店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1405,7 +1409,7 @@
         <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1419,7 +1423,7 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
@@ -1431,7 +1435,7 @@
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1466,34 +1470,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7326770712952178688</t>
+          <t>6756124064592545806</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IU酒店（晋中榆次五中万达广场店）</t>
+          <t>希岸酒店(长治城隍庙店)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IU酒店(晋中榆次五中万达广场店)</t>
+          <t>希岸酒店(长治城隍庙店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1574,7 +1578,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1904,40 +1908,36 @@
           <t>山西中片区</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>晋中市</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6601135743966382093</t>
+          <t>6601152258656716808</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>希岸酒店(晋中大学城万达店)</t>
+          <t>7天酒店(长治西大街上党门店)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>希岸酒店(晋中大学城万达店)</t>
+          <t>7天连锁酒店(长治西大街上党门店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1947,13 +1947,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -1999,17 +1999,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7546085742750779430</t>
+          <t>6601135743966382093</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>麗枫酒店（晋中太谷金谷广场店）</t>
+          <t>希岸酒店(晋中大学城万达店)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>麗枫酒店(晋中太谷金谷广场店)</t>
+          <t>希岸酒店(晋中大学城万达店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2021,11 +2021,11 @@
         <v>92</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2035,25 +2035,25 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
+        <v>22</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30</v>
+      </c>
+      <c r="O17" t="n">
         <v>25</v>
       </c>
-      <c r="N17" t="n">
-        <v>30</v>
-      </c>
-      <c r="O17" t="n">
-        <v>20</v>
-      </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T17" t="n">
         <v>20</v>
@@ -2087,33 +2087,33 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7042658998100690983</t>
+          <t>7546085742750779430</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IU酒店（晋中第一人民医院店）</t>
+          <t>麗枫酒店（晋中太谷金谷广场店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IU酒店(晋中第一人民医院店)</t>
+          <t>麗枫酒店(晋中太谷金谷广场店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2141,7 +2141,7 @@
         <v>30</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T18" t="n">
         <v>20</v>
@@ -2170,27 +2170,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6756124064592545806</t>
+          <t>7042658998100690983</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>希岸酒店(长治城隍庙店)</t>
+          <t>IU酒店（晋中第一人民医院店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>希岸酒店(长治城隍庙店)</t>
+          <t>IU酒店(晋中第一人民医院店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2217,13 +2217,13 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2263,29 +2263,29 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6845633128015398912</t>
+          <t>7418425551997650980</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>希岸酒店(长治壶关县八泉峡欢乐谷店)</t>
+          <t>IU酒店（长治通天峡景区店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>希岸酒店(壶关店)</t>
+          <t>IU酒店(长治通天峡景区店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>95</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
+        <v>20</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30</v>
+      </c>
+      <c r="O20" t="n">
         <v>25</v>
-      </c>
-      <c r="N20" t="n">
-        <v>30</v>
-      </c>
-      <c r="O20" t="n">
-        <v>20</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
@@ -2346,22 +2346,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7370927881465104420</t>
+          <t>6845633128015398912</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（晋中榆社文峰塔店）</t>
+          <t>希岸酒店(长治壶关县八泉峡欢乐谷店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(榆社店)</t>
+          <t>希岸酒店(壶关店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2373,7 +2373,7 @@
         <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2393,13 +2393,13 @@
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2439,33 +2439,33 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6954291220742932518</t>
+          <t>7370927881465104420</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（山西师范武宿机场店）</t>
+          <t>维也纳3好酒店（晋中榆社文峰塔店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(山西榆次大学城店)</t>
+          <t>维也纳3好酒店(榆社店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -2527,17 +2527,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7099019942820841472</t>
+          <t>6954291220742932518</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0晋中大学城店）</t>
+          <t>维也纳智好酒店（山西师范武宿机场店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳酒店5.0山西晋中大学城店</t>
+          <t>维也纳智好酒店(山西榆次大学城店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2549,7 +2549,7 @@
         <v>95</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6601144225092339716</t>
+          <t>7099019942820841472</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>锦江之星(平遥古城店)</t>
+          <t>维也纳酒店（5.0晋中大学城店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>锦江之星酒店(平遥古城店)</t>
+          <t>维也纳酒店5.0山西晋中大学城店</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2651,7 +2651,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2663,7 +2663,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2698,31 +2698,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7067092710515017740</t>
+          <t>6601144225092339716</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7天优品Premium（长治壶关新建南路店）</t>
+          <t>锦江之星(平遥古城店)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7天优品酒店(长治壶关新建南路店)</t>
+          <t>锦江之星酒店(平遥古城店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
@@ -2786,38 +2786,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6830714497225984000</t>
+          <t>7067092710515017740</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7天优品（晋中介休火车站绵山南街店）</t>
+          <t>7天优品Premium（长治壶关新建南路店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7天优品(晋中介休火车站绵山南街店)</t>
+          <t>7天优品酒店(长治壶关新建南路店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2827,13 +2827,13 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
@@ -2874,22 +2874,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7232160323472459834</t>
+          <t>6830714497225984000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7天酒店（长治上党区凯德世家广场店）</t>
+          <t>7天优品（晋中介休火车站绵山南街店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7天酒店(长治上党区府后东街店)</t>
+          <t>7天优品(晋中介休火车站绵山南街店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2915,7 +2915,7 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2927,7 +2927,7 @@
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7418425551997650980</t>
+          <t>7232160323472459834</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IU酒店（长治通天峡景区店）</t>
+          <t>7天酒店（长治上党区凯德世家广场店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>IU酒店(长治通天峡景区店)</t>
+          <t>7天酒店(长治上党区府后东街店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2989,11 +2989,11 @@
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3003,19 +3003,19 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3398,54 +3398,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7637699073047873570</t>
+          <t>7137101215036344334</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>麗枫酒店（长治东站八一广场店）</t>
+          <t>7天优品Premium（山西晋中太谷店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>麗枫酒店(长治东站八一广场店)</t>
+          <t>7天优品Premium(山西晋中太谷店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>提质量,附加分,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
         <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
@@ -3457,7 +3457,7 @@
         <v>30</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="n">
         <v>20</v>
@@ -3486,22 +3486,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7137101215036344334</t>
+          <t>7320489581046925352</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7天优品Premium（山西晋中太谷店）</t>
+          <t>维也纳酒店（5.0长治学院高铁东站店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7天优品Premium(山西晋中太谷店)</t>
+          <t>维也纳酒店(长治学院店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3510,36 +3510,36 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I34" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L34" t="n">
         <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N34" t="n">
         <v>30</v>
       </c>
       <c r="O34" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P34" t="n">
         <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R34" t="n">
         <v>30</v>
@@ -3579,33 +3579,33 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>7320489581046925352</t>
+          <t>7637699073047873570</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0长治学院高铁东站店）</t>
+          <t>麗枫酒店（长治东站八一广场店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>维也纳酒店(长治学院店)</t>
+          <t>麗枫酒店(长治东站八一广场店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>102</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3615,25 +3615,25 @@
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N35" t="n">
         <v>30</v>
       </c>
       <c r="O35" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P35" t="n">
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T35" t="n">
         <v>20</v>
@@ -4217,7 +4217,7 @@
         <v>110</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H43" t="n">
